--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1610,7 +1610,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm , Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1725,7 +1725,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1840,7 +1840,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1955,7 +1955,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -3172,7 +3172,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3395,7 +3395,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flarktjärnen, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -3953,7 +3953,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -4064,7 +4064,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flarktjärnen, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4175,7 +4175,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flarktjärnen, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -7871,7 +7871,7 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -7986,7 +7986,7 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -10881,7 +10881,7 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -10996,7 +10996,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -11111,7 +11111,7 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -11226,7 +11226,7 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -11338,7 +11338,7 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -11449,7 +11449,7 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Flarktjärnen, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -14332,7 +14332,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
@@ -18832,7 +18832,7 @@
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
@@ -18947,7 +18947,7 @@
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
@@ -19059,7 +19059,7 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
@@ -19170,7 +19170,7 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Flarktjärnen sv, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure korsningen Långviken avvanm_prio 1_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
@@ -21384,7 +21384,7 @@
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
@@ -21499,7 +21499,7 @@
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
@@ -21614,7 +21614,7 @@
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
@@ -21729,7 +21729,7 @@
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>S om Kvarntjärnen, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure korsningen Långviken avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q189" t="n">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -7186,6 +7186,9 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Söder om Kvarntjärn, Söder om Kvarntjärn, Pi lm</t>
@@ -7246,6 +7249,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7260,7 +7264,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -15904,7 +15904,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Äldre ringhack bild</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -6475,7 +6475,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Martin Axegård, anders tedeholm, Benny Öwre, Ulrika Karlsson</t>
+          <t>Christina Boyd, Ulrika Karlsson, Benny Öwre, anders tedeholm, Martin Axegård, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd, Martin Axegård, Jörgen Sundin, Benny Öwre, per-erik mukka, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Alva Danielsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Elin Kannerby, anders tedeholm, Alva Danielsson, Alva Dahlqvist Cederstrand, Ulrika Karlsson, per-erik mukka, Benny Öwre, Jörgen Sundin, Martin Axegård</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Ulrika Karlsson, Jörgen Sundin, Alva Dahlqvist Cederstrand, Alva Danielsson, Martin Axegård, Tyr Nilsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Benny Öwre</t>
+          <t>Christina Boyd, Benny Öwre, Anton Lundberg, Elin Kannerby, anders tedeholm, Tyr Nilsson, Martin Axegård, Alva Danielsson, Alva Dahlqvist Cederstrand, Jörgen Sundin, Ulrika Karlsson, per-erik mukka</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AZ189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297929</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303115</t>
         </is>
       </c>
     </row>
@@ -1339,6 +1369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295629</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293571</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294542</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1803,6 +1853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294551</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294553</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294556</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,6 +2209,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295605</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295610</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2366,6 +2441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295615</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2477,6 +2557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295616</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295617</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2695,6 +2785,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302472</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2802,6 +2897,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302478</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303116</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303118</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3133,6 +3243,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295582</t>
         </is>
       </c>
     </row>
@@ -3250,6 +3365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294545</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3361,6 +3481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295622</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294740</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3583,6 +3713,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295289</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3694,6 +3829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303106</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3803,6 +3943,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295633</t>
         </is>
       </c>
     </row>
@@ -3919,6 +4064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293572</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4030,6 +4180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294737</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4141,6 +4296,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294739</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4252,6 +4412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294741</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4363,6 +4528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295575</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4475,6 +4645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295603</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4586,6 +4761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295620</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4697,6 +4877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295631</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4808,6 +4993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297947</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4915,6 +5105,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302464</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5024,6 +5219,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297942</t>
         </is>
       </c>
     </row>
@@ -5140,6 +5340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293577</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5251,6 +5456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295580</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5362,6 +5572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295586</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5473,6 +5688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297952</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5580,6 +5800,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302490</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5695,6 +5920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294249</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5810,6 +6040,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296757</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5921,6 +6156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297946</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6032,6 +6272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298726</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6141,6 +6386,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298730</t>
         </is>
       </c>
     </row>
@@ -6257,6 +6507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293568</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6366,6 +6621,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295584</t>
         </is>
       </c>
     </row>
@@ -6475,12 +6735,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Christina Boyd, Ulrika Karlsson, Benny Öwre, anders tedeholm, Martin Axegård, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Martin Axegård, anders tedeholm, Benny Öwre, Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294242</t>
         </is>
       </c>
     </row>
@@ -6598,6 +6863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294245</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6710,6 +6980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294559</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6821,6 +7096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295623</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6932,6 +7212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303117</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7043,6 +7328,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303129</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7152,6 +7442,11 @@
       <c r="AY59" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303132</t>
         </is>
       </c>
     </row>
@@ -7269,6 +7564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135304947</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7383,6 +7683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293570</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7497,6 +7802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293573</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7604,12 +7914,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Elin Kannerby, anders tedeholm, Alva Danielsson, Alva Dahlqvist Cederstrand, Ulrika Karlsson, per-erik mukka, Benny Öwre, Jörgen Sundin, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Jörgen Sundin, Benny Öwre, per-erik mukka, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Alva Danielsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294234</t>
         </is>
       </c>
     </row>
@@ -7727,6 +8042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294236</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7842,6 +8162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294243</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7957,6 +8282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294544</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8072,6 +8402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294549</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8183,6 +8518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295281</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8294,6 +8634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295287</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8405,6 +8750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295609</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8516,6 +8866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295612</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8627,6 +8982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298729</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8734,6 +9094,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302465</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8841,6 +9206,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302470</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8948,6 +9318,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302487</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9059,6 +9434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303107</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9170,6 +9550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303112</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9281,6 +9666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303127</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9392,6 +9782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303128</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9499,6 +9894,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302491</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9610,6 +10010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295632</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9717,6 +10122,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302485</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9827,6 +10237,11 @@
       <c r="AY83" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303124</t>
         </is>
       </c>
     </row>
@@ -9943,6 +10358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293569</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10057,6 +10477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293576</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10171,6 +10596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293578</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10285,6 +10715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293580</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10392,12 +10827,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294227</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10947,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Christina Boyd, Benny Öwre, Anton Lundberg, Elin Kannerby, anders tedeholm, Tyr Nilsson, Martin Axegård, Alva Danielsson, Alva Dahlqvist Cederstrand, Jörgen Sundin, Ulrika Karlsson, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Ulrika Karlsson, Jörgen Sundin, Alva Dahlqvist Cederstrand, Alva Danielsson, Martin Axegård, Tyr Nilsson, anders tedeholm, Elin Kannerby, Anton Lundberg, Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294232</t>
         </is>
       </c>
     </row>
@@ -10622,6 +11067,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294235</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10737,6 +11187,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294244</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10852,6 +11307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294246</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10967,6 +11427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294546</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11082,6 +11547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294550</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11197,6 +11667,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294555</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11312,6 +11787,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294560</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11423,6 +11903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294735</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11534,6 +12019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294738</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11645,6 +12135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295283</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11756,6 +12251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295285</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11867,6 +12367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295290</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11978,6 +12483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295611</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12089,6 +12599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295614</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12200,6 +12715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295619</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12309,6 +12829,11 @@
       <c r="AY105" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295625</t>
         </is>
       </c>
     </row>
@@ -12426,6 +12951,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296754</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12537,6 +13067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297927</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12648,6 +13183,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297931</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12759,6 +13299,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297939</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12870,6 +13415,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297945</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12981,6 +13531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297948</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13092,6 +13647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297951</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13203,6 +13763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297953</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13314,6 +13879,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298723</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13426,6 +13996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298731</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13533,6 +14108,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302486</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13640,6 +14220,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302489</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13747,6 +14332,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302493</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13858,6 +14448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303126</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13969,6 +14564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297925</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14080,6 +14680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297928</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14196,6 +14801,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297944</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14303,6 +14913,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302494</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14418,6 +15033,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294554</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14529,6 +15149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295621</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14638,6 +15263,11 @@
       <c r="AY126" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295627</t>
         </is>
       </c>
     </row>
@@ -14755,6 +15385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296755</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14866,6 +15501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297943</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14973,6 +15613,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302471</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15092,6 +15737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293566</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15211,6 +15861,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293583</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15330,6 +15985,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293584</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15449,6 +16109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293585</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15568,6 +16233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293586</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15687,6 +16357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293587</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15808,6 +16483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294729</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15932,6 +16612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297936</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16056,6 +16741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297937</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16180,6 +16870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297954</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16300,6 +16995,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302457</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16420,6 +17120,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302466</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16537,6 +17242,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302468</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16653,6 +17363,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298724</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16769,6 +17484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298725</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16881,6 +17601,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302474</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16992,6 +17717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297938</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17120,6 +17850,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297940</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17236,6 +17971,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302482</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17352,6 +18092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293575</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17463,6 +18208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295576</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17570,6 +18320,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294238</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17678,12 +18433,17 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294226</t>
         </is>
       </c>
     </row>
@@ -17802,6 +18562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294240</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17913,6 +18678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295286</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18024,6 +18794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295608</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18135,6 +18910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297932</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18246,6 +19026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298727</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18357,6 +19142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298728</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18468,6 +19258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298732</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18579,6 +19374,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303130</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18691,6 +19491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295624</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18801,6 +19606,11 @@
       <c r="AY162" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295626</t>
         </is>
       </c>
     </row>
@@ -18918,6 +19728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294547</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19033,6 +19848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294561</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19144,6 +19964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294730</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19255,6 +20080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294732</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19366,6 +20196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295599</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19477,6 +20312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295628</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19588,6 +20428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295630</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19699,6 +20544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297924</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19806,6 +20656,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302476</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19913,6 +20768,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302479</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20020,6 +20880,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302480</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20127,6 +20992,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302481</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20242,6 +21112,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303108</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20351,6 +21226,11 @@
       <c r="AY176" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303113</t>
         </is>
       </c>
     </row>
@@ -20467,6 +21347,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293567</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20578,6 +21463,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295600</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20694,6 +21584,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298722</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20805,6 +21700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303111</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20916,6 +21816,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303120</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21027,6 +21932,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303121</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21138,6 +22048,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303123</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21249,6 +22164,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303125</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21358,6 +22278,11 @@
       <c r="AY185" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135303131</t>
         </is>
       </c>
     </row>
@@ -21475,6 +22400,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294548</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21590,6 +22520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294552</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21705,6 +22640,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294558</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21820,8 +22760,203 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294562</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård, Christina Boyd, anders tedeholm, Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
+          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135294734</v>
       </c>
       <c r="B4" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1023,7 +1023,7 @@
         <v>135297929</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135303115</v>
       </c>
       <c r="B6" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>135297950</v>
       </c>
       <c r="B7" t="n">
-        <v>92235</v>
+        <v>92277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135295629</v>
       </c>
       <c r="B8" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135293571</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135294542</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135294551</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>135294553</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135294556</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135295605</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135295610</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>135295615</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135295616</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135295617</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135302472</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135302478</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135303116</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>135303118</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135295582</v>
       </c>
       <c r="B23" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>135294545</v>
       </c>
       <c r="B24" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135295622</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>135294740</v>
       </c>
       <c r="B26" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård, Christina Boyd, anders tedeholm, Ulrika Karlsson</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3608,7 +3608,7 @@
         <v>135295289</v>
       </c>
       <c r="B27" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3724,7 +3724,7 @@
         <v>135303106</v>
       </c>
       <c r="B28" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135295633</v>
       </c>
       <c r="B29" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>135293572</v>
       </c>
       <c r="B30" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135294737</v>
       </c>
       <c r="B31" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>135294739</v>
       </c>
       <c r="B32" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>135294741</v>
       </c>
       <c r="B33" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>135295575</v>
       </c>
       <c r="B34" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>135295603</v>
       </c>
       <c r="B35" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135295620</v>
       </c>
       <c r="B36" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135295631</v>
       </c>
       <c r="B37" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135297947</v>
       </c>
       <c r="B38" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135302464</v>
       </c>
       <c r="B39" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135297942</v>
       </c>
       <c r="B40" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135293577</v>
       </c>
       <c r="B41" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>135295580</v>
       </c>
       <c r="B42" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135295586</v>
       </c>
       <c r="B43" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135297952</v>
       </c>
       <c r="B44" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>135302490</v>
       </c>
       <c r="B45" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>135294249</v>
       </c>
       <c r="B46" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>135296757</v>
       </c>
       <c r="B47" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135297946</v>
       </c>
       <c r="B48" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135298726</v>
       </c>
       <c r="B49" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135298730</v>
       </c>
       <c r="B50" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>135293568</v>
       </c>
       <c r="B51" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>135295584</v>
       </c>
       <c r="B52" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>135294242</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>135294245</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>135294559</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>135295623</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>135303117</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>135303129</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>135303132</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>135304947</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135293570</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135293573</v>
       </c>
       <c r="B62" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>135294234</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135294236</v>
       </c>
       <c r="B64" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>135294243</v>
       </c>
       <c r="B65" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135294544</v>
       </c>
       <c r="B66" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>135294549</v>
       </c>
       <c r="B67" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135295281</v>
       </c>
       <c r="B68" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8529,7 +8529,7 @@
         <v>135295287</v>
       </c>
       <c r="B69" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>135295609</v>
       </c>
       <c r="B70" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>135295612</v>
       </c>
       <c r="B71" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>135298729</v>
       </c>
       <c r="B72" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>135302465</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>135302470</v>
       </c>
       <c r="B74" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135302487</v>
       </c>
       <c r="B75" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>135303107</v>
       </c>
       <c r="B76" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135303112</v>
       </c>
       <c r="B77" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>135303127</v>
       </c>
       <c r="B78" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>135303128</v>
       </c>
       <c r="B79" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>135302491</v>
       </c>
       <c r="B80" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>135295632</v>
       </c>
       <c r="B81" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>135302485</v>
       </c>
       <c r="B82" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>135303124</v>
       </c>
       <c r="B83" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>135293569</v>
       </c>
       <c r="B84" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>135293576</v>
       </c>
       <c r="B85" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>135293578</v>
       </c>
       <c r="B86" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>135293580</v>
       </c>
       <c r="B87" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135294227</v>
       </c>
       <c r="B88" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>135294232</v>
       </c>
       <c r="B89" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135294235</v>
       </c>
       <c r="B90" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>135294244</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>135294246</v>
       </c>
       <c r="B92" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>135294546</v>
       </c>
       <c r="B93" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>135294550</v>
       </c>
       <c r="B94" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>135294555</v>
       </c>
       <c r="B95" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>135294560</v>
       </c>
       <c r="B96" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135294735</v>
       </c>
       <c r="B97" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11914,7 +11914,7 @@
         <v>135294738</v>
       </c>
       <c r="B98" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Benny Öwre, Martin Axegård, per-erik mukka, Tyr Nilsson, Jörgen Sundin, Elin Kannerby, Alva Danielsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Ulrika Karlsson, anders tedeholm, Christina Boyd</t>
+          <t>Benny Öwre, Christina Boyd, anders tedeholm, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12030,7 +12030,7 @@
         <v>135295283</v>
       </c>
       <c r="B99" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12146,7 +12146,7 @@
         <v>135295285</v>
       </c>
       <c r="B100" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>135295290</v>
       </c>
       <c r="B101" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>135295611</v>
       </c>
       <c r="B102" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>135295614</v>
       </c>
       <c r="B103" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>135295619</v>
       </c>
       <c r="B104" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>135295625</v>
       </c>
       <c r="B105" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>135296754</v>
       </c>
       <c r="B106" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>135297927</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>135297931</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>135297939</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>135297945</v>
       </c>
       <c r="B110" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135297948</v>
       </c>
       <c r="B111" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>135297951</v>
       </c>
       <c r="B112" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>135297953</v>
       </c>
       <c r="B113" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>135298723</v>
       </c>
       <c r="B114" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>135298731</v>
       </c>
       <c r="B115" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>135302486</v>
       </c>
       <c r="B116" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>135302489</v>
       </c>
       <c r="B117" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>135302493</v>
       </c>
       <c r="B118" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>135303126</v>
       </c>
       <c r="B119" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>135297925</v>
       </c>
       <c r="B120" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>135297928</v>
       </c>
       <c r="B121" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>135297944</v>
       </c>
       <c r="B122" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>135302494</v>
       </c>
       <c r="B123" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>135294554</v>
       </c>
       <c r="B124" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135295621</v>
       </c>
       <c r="B125" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>135295627</v>
       </c>
       <c r="B126" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>135296755</v>
       </c>
       <c r="B127" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>135297943</v>
       </c>
       <c r="B128" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>135302471</v>
       </c>
       <c r="B129" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>135293566</v>
       </c>
       <c r="B130" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>135293583</v>
       </c>
       <c r="B131" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>135293584</v>
       </c>
       <c r="B132" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>135293585</v>
       </c>
       <c r="B133" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>135293586</v>
       </c>
       <c r="B134" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>135293587</v>
       </c>
       <c r="B135" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>135294729</v>
       </c>
       <c r="B136" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135297936</v>
       </c>
       <c r="B137" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>135297937</v>
       </c>
       <c r="B138" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>135297954</v>
       </c>
       <c r="B139" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>135302457</v>
       </c>
       <c r="B140" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>135302466</v>
       </c>
       <c r="B141" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>135302468</v>
       </c>
       <c r="B142" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>135298724</v>
       </c>
       <c r="B143" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>135298725</v>
       </c>
       <c r="B144" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>135302474</v>
       </c>
       <c r="B145" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>135297938</v>
       </c>
       <c r="B146" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>135297940</v>
       </c>
       <c r="B147" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>135302482</v>
       </c>
       <c r="B148" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>135293575</v>
       </c>
       <c r="B149" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>135295576</v>
       </c>
       <c r="B150" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>135294238</v>
       </c>
       <c r="B151" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>135294226</v>
       </c>
       <c r="B152" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>135294240</v>
       </c>
       <c r="B153" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>135295286</v>
       </c>
       <c r="B154" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>135295608</v>
       </c>
       <c r="B155" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>135297932</v>
       </c>
       <c r="B156" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>135298727</v>
       </c>
       <c r="B157" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>135298728</v>
       </c>
       <c r="B158" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>135298732</v>
       </c>
       <c r="B159" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>135303130</v>
       </c>
       <c r="B160" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>135295624</v>
       </c>
       <c r="B161" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>135295626</v>
       </c>
       <c r="B162" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>135294547</v>
       </c>
       <c r="B163" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>135294561</v>
       </c>
       <c r="B164" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>135294730</v>
       </c>
       <c r="B165" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>135294732</v>
       </c>
       <c r="B166" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>135295599</v>
       </c>
       <c r="B167" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>135295628</v>
       </c>
       <c r="B168" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>135295630</v>
       </c>
       <c r="B169" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>135297924</v>
       </c>
       <c r="B170" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>135302476</v>
       </c>
       <c r="B171" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>135302479</v>
       </c>
       <c r="B172" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>135302480</v>
       </c>
       <c r="B173" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>135302481</v>
       </c>
       <c r="B174" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>135303108</v>
       </c>
       <c r="B175" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>135303113</v>
       </c>
       <c r="B176" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>135293567</v>
       </c>
       <c r="B177" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>135295600</v>
       </c>
       <c r="B178" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>135298722</v>
       </c>
       <c r="B179" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>135303111</v>
       </c>
       <c r="B180" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>135303120</v>
       </c>
       <c r="B181" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>135303121</v>
       </c>
       <c r="B182" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>135303123</v>
       </c>
       <c r="B183" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>135303125</v>
       </c>
       <c r="B184" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>135303131</v>
       </c>
       <c r="B185" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>135294548</v>
       </c>
       <c r="B186" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>135294552</v>
       </c>
       <c r="B187" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>135294558</v>
       </c>
       <c r="B188" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>135294562</v>
       </c>
       <c r="B189" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135294734</v>
       </c>
       <c r="B4" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>135297929</v>
       </c>
       <c r="B5" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135303115</v>
       </c>
       <c r="B6" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>135297950</v>
       </c>
       <c r="B7" t="n">
-        <v>92277</v>
+        <v>92304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135295629</v>
       </c>
       <c r="B8" t="n">
-        <v>83393</v>
+        <v>83420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>135293571</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>135294542</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>135294551</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>135294553</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135294556</v>
       </c>
       <c r="B13" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135295605</v>
       </c>
       <c r="B14" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135295610</v>
       </c>
       <c r="B15" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>135295615</v>
       </c>
       <c r="B16" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>135295616</v>
       </c>
       <c r="B17" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>135295617</v>
       </c>
       <c r="B18" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>135302472</v>
       </c>
       <c r="B19" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135302478</v>
       </c>
       <c r="B20" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>135303116</v>
       </c>
       <c r="B21" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>135303118</v>
       </c>
       <c r="B22" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135295582</v>
       </c>
       <c r="B23" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>135294545</v>
       </c>
       <c r="B24" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135295622</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>135294740</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>135295289</v>
       </c>
       <c r="B27" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135303106</v>
       </c>
       <c r="B28" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135295633</v>
       </c>
       <c r="B29" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>135293572</v>
       </c>
       <c r="B30" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135294737</v>
       </c>
       <c r="B31" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>135294739</v>
       </c>
       <c r="B32" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>135294741</v>
       </c>
       <c r="B33" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>135295575</v>
       </c>
       <c r="B34" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>135295603</v>
       </c>
       <c r="B35" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135295620</v>
       </c>
       <c r="B36" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135295631</v>
       </c>
       <c r="B37" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135297947</v>
       </c>
       <c r="B38" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135302464</v>
       </c>
       <c r="B39" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135297942</v>
       </c>
       <c r="B40" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135293577</v>
       </c>
       <c r="B41" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>135295580</v>
       </c>
       <c r="B42" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135295586</v>
       </c>
       <c r="B43" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135297952</v>
       </c>
       <c r="B44" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>135302490</v>
       </c>
       <c r="B45" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>135294249</v>
       </c>
       <c r="B46" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>135296757</v>
       </c>
       <c r="B47" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135297946</v>
       </c>
       <c r="B48" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135298726</v>
       </c>
       <c r="B49" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135298730</v>
       </c>
       <c r="B50" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>135293568</v>
       </c>
       <c r="B51" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>135295584</v>
       </c>
       <c r="B52" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>135294242</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>135294245</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>135294559</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>135295623</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>135303117</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>135303129</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>135303132</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>135304947</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135293570</v>
       </c>
       <c r="B61" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>135293573</v>
       </c>
       <c r="B62" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>135294234</v>
       </c>
       <c r="B63" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135294236</v>
       </c>
       <c r="B64" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>135294243</v>
       </c>
       <c r="B65" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135294544</v>
       </c>
       <c r="B66" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>135294549</v>
       </c>
       <c r="B67" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135295281</v>
       </c>
       <c r="B68" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>135295287</v>
       </c>
       <c r="B69" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>135295609</v>
       </c>
       <c r="B70" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>135295612</v>
       </c>
       <c r="B71" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>135298729</v>
       </c>
       <c r="B72" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>135302465</v>
       </c>
       <c r="B73" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>135302470</v>
       </c>
       <c r="B74" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135302487</v>
       </c>
       <c r="B75" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>135303107</v>
       </c>
       <c r="B76" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135303112</v>
       </c>
       <c r="B77" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>135303127</v>
       </c>
       <c r="B78" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>135303128</v>
       </c>
       <c r="B79" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>135302491</v>
       </c>
       <c r="B80" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>135295632</v>
       </c>
       <c r="B81" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>135302485</v>
       </c>
       <c r="B82" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>135303124</v>
       </c>
       <c r="B83" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>135293569</v>
       </c>
       <c r="B84" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>135293576</v>
       </c>
       <c r="B85" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>135293578</v>
       </c>
       <c r="B86" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>135293580</v>
       </c>
       <c r="B87" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135294227</v>
       </c>
       <c r="B88" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>135294232</v>
       </c>
       <c r="B89" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>135294235</v>
       </c>
       <c r="B90" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>135294244</v>
       </c>
       <c r="B91" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>135294246</v>
       </c>
       <c r="B92" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>135294546</v>
       </c>
       <c r="B93" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>135294550</v>
       </c>
       <c r="B94" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>135294555</v>
       </c>
       <c r="B95" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>135294560</v>
       </c>
       <c r="B96" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>135294735</v>
       </c>
       <c r="B97" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135294738</v>
       </c>
       <c r="B98" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>135295283</v>
       </c>
       <c r="B99" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>135295285</v>
       </c>
       <c r="B100" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>135295290</v>
       </c>
       <c r="B101" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>135295611</v>
       </c>
       <c r="B102" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>135295614</v>
       </c>
       <c r="B103" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>135295619</v>
       </c>
       <c r="B104" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>135295625</v>
       </c>
       <c r="B105" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>135296754</v>
       </c>
       <c r="B106" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>135297927</v>
       </c>
       <c r="B107" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>135297931</v>
       </c>
       <c r="B108" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>135297939</v>
       </c>
       <c r="B109" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>135297945</v>
       </c>
       <c r="B110" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>135297948</v>
       </c>
       <c r="B111" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>135297951</v>
       </c>
       <c r="B112" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>135297953</v>
       </c>
       <c r="B113" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>135298723</v>
       </c>
       <c r="B114" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>135298731</v>
       </c>
       <c r="B115" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>135302486</v>
       </c>
       <c r="B116" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>135302489</v>
       </c>
       <c r="B117" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>135302493</v>
       </c>
       <c r="B118" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>135303126</v>
       </c>
       <c r="B119" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>135297925</v>
       </c>
       <c r="B120" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>135297928</v>
       </c>
       <c r="B121" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>135297944</v>
       </c>
       <c r="B122" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>135302494</v>
       </c>
       <c r="B123" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>135294554</v>
       </c>
       <c r="B124" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>135295621</v>
       </c>
       <c r="B125" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>135295627</v>
       </c>
       <c r="B126" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>135296755</v>
       </c>
       <c r="B127" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>135297943</v>
       </c>
       <c r="B128" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>135302471</v>
       </c>
       <c r="B129" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>135294238</v>
       </c>
       <c r="B151" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>135294226</v>
       </c>
       <c r="B152" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>135294240</v>
       </c>
       <c r="B153" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>135295286</v>
       </c>
       <c r="B154" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>135295608</v>
       </c>
       <c r="B155" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>135297932</v>
       </c>
       <c r="B156" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>135298727</v>
       </c>
       <c r="B157" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>135298728</v>
       </c>
       <c r="B158" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>135298732</v>
       </c>
       <c r="B159" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>135303130</v>
       </c>
       <c r="B160" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>135295624</v>
       </c>
       <c r="B161" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>135295626</v>
       </c>
       <c r="B162" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>135294547</v>
       </c>
       <c r="B163" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>135294561</v>
       </c>
       <c r="B164" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>135294730</v>
       </c>
       <c r="B165" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>135294732</v>
       </c>
       <c r="B166" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>135295599</v>
       </c>
       <c r="B167" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>135295628</v>
       </c>
       <c r="B168" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>135295630</v>
       </c>
       <c r="B169" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>135297924</v>
       </c>
       <c r="B170" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>135302476</v>
       </c>
       <c r="B171" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>135302479</v>
       </c>
       <c r="B172" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>135302480</v>
       </c>
       <c r="B173" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>135302481</v>
       </c>
       <c r="B174" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>135303108</v>
       </c>
       <c r="B175" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>135303113</v>
       </c>
       <c r="B176" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>135293567</v>
       </c>
       <c r="B177" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>135295600</v>
       </c>
       <c r="B178" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>135298722</v>
       </c>
       <c r="B179" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>135303111</v>
       </c>
       <c r="B180" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>135303120</v>
       </c>
       <c r="B181" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>135303121</v>
       </c>
       <c r="B182" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>135303123</v>
       </c>
       <c r="B183" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>135303125</v>
       </c>
       <c r="B184" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>135303131</v>
       </c>
       <c r="B185" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>135294548</v>
       </c>
       <c r="B186" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>135294552</v>
       </c>
       <c r="B187" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>135294558</v>
       </c>
       <c r="B188" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>135294562</v>
       </c>
       <c r="B189" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294247</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135294248</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135294734</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>135297929</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135303115</v>
       </c>
       <c r="B6" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>135297950</v>
       </c>
       <c r="B7" t="n">
-        <v>92309</v>
+        <v>92311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135295622</v>
       </c>
       <c r="B25" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>135294740</v>
       </c>
       <c r="B26" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>135295289</v>
       </c>
       <c r="B27" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135303106</v>
       </c>
       <c r="B28" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>135293572</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>135294737</v>
       </c>
       <c r="B31" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>135294739</v>
       </c>
       <c r="B32" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>135294741</v>
       </c>
       <c r="B33" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>135295575</v>
       </c>
       <c r="B34" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>135295603</v>
       </c>
       <c r="B35" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>135295620</v>
       </c>
       <c r="B36" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>135295631</v>
       </c>
       <c r="B37" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>135297947</v>
       </c>
       <c r="B38" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>135302464</v>
       </c>
       <c r="B39" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>135297942</v>
       </c>
       <c r="B40" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>135293577</v>
       </c>
       <c r="B41" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>135295580</v>
       </c>
       <c r="B42" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>135295586</v>
       </c>
       <c r="B43" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>135297952</v>
       </c>
       <c r="B44" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>135302490</v>
       </c>
       <c r="B45" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>135294249</v>
       </c>
       <c r="B46" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>135296757</v>
       </c>
       <c r="B47" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>135297946</v>
       </c>
       <c r="B48" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135298726</v>
       </c>
       <c r="B49" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>135298730</v>
       </c>
       <c r="B50" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>135293568</v>
       </c>
       <c r="B51" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>135295584</v>
       </c>
       <c r="B52" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>135294238</v>
       </c>
       <c r="B151" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>135294226</v>
       </c>
       <c r="B152" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>135294240</v>
       </c>
       <c r="B153" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>135295286</v>
       </c>
       <c r="B154" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>135295608</v>
       </c>
       <c r="B155" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>135297932</v>
       </c>
       <c r="B156" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>135298727</v>
       </c>
       <c r="B157" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>135298728</v>
       </c>
       <c r="B158" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>135298732</v>
       </c>
       <c r="B159" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>135303130</v>
       </c>
       <c r="B160" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -10827,7 +10827,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Jörgen Sundin, anders tedeholm, Elin Kannerby, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Tyr Nilsson</t>
+          <t>Christina Boyd, Tyr Nilsson, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Elin Kannerby, anders tedeholm, Jörgen Sundin, Benny Öwre, Ulrika Karlsson, Martin Axegård, per-erik mukka</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Jörgen Sundin, Ulrika Karlsson, Elin Kannerby, Benny Öwre, anders tedeholm, Tyr Nilsson, Alva Danielsson, Alva Dahlqvist Cederstrand, Anton Lundberg, Martin Axegård</t>
+          <t>Christina Boyd, Martin Axegård, Anton Lundberg, Alva Dahlqvist Cederstrand, Alva Danielsson, Tyr Nilsson, anders tedeholm, Benny Öwre, Elin Kannerby, Ulrika Karlsson, Jörgen Sundin, per-erik mukka</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">

--- a/artfynd/A 30870-2023 artfynd.xlsx
+++ b/artfynd/A 30870-2023 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>135297950</v>
       </c>
       <c r="B7" t="n">
-        <v>92311</v>
+        <v>92325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>135297936</v>
       </c>
       <c r="B137" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
